--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_metropolitana.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:44</t>
+    <t xml:space="preserve">2026-09-09 20:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_metropolitana.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Provincial" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Provincial_sexo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Tramo_etario" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tramo_etario_nacional" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Media_nacional" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Provincial_sexo" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Tramo_etario" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Tramo_etario_nacional" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Tramo_etario_nacional'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Tramo_etario_nacional'!$A$1:$C$8</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -69,7 +70,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:49</t>
+    <t xml:space="preserve">2026-09-18 10:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -96,6 +97,9 @@
     <t xml:space="preserve">Año</t>
   </si>
   <si>
+    <t xml:space="preserve">Media nacional (%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mujeres (%)</t>
   </si>
   <si>
@@ -127,9 +131,6 @@
   </si>
   <si>
     <t xml:space="preserve">16 a 17 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media nacional (%)</t>
   </si>
 </sst>
 </file>
@@ -858,6 +859,62 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>58.44</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>94.28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>86.91</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>43.38</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
@@ -871,10 +928,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
@@ -1220,7 +1277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -1239,52 +1296,52 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>16.35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>46.25</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>90.6</v>
+        <v>88.25</v>
       </c>
     </row>
     <row r="5">
@@ -1295,7 +1352,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>19.77</v>
@@ -1309,7 +1366,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>51.33</v>
@@ -1323,7 +1380,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>93.72</v>
@@ -1331,128 +1388,128 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>15.9</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>48.91</v>
+        <v>46.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>92.54</v>
+        <v>90.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>17.11</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>47.24</v>
+        <v>48.91</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>92.13</v>
+        <v>92.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>18</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>46.15</v>
+        <v>47.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>88.25</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="17">
@@ -1463,7 +1520,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>17.84</v>
@@ -1477,7 +1534,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>52.74</v>
@@ -1491,7 +1548,7 @@
         <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>94.19</v>
@@ -1499,30 +1556,30 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>94.11</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>94.01</v>
+        <v>92.94</v>
       </c>
     </row>
     <row r="22">
@@ -1533,7 +1590,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>94.58</v>
@@ -1547,7 +1604,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>96.08</v>
@@ -1555,86 +1612,86 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>93.62</v>
+        <v>94.11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>95.11</v>
+        <v>94.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>93.86</v>
+        <v>93.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>95.75</v>
+        <v>95.11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>92.8</v>
+        <v>93.86</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>92.94</v>
+        <v>95.75</v>
       </c>
     </row>
     <row r="30">
@@ -1645,7 +1702,7 @@
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>94.05</v>
@@ -1659,7 +1716,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>96</v>
@@ -1667,30 +1724,30 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>80.68</v>
+        <v>84.43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>88.53</v>
+        <v>87.38</v>
       </c>
     </row>
     <row r="34">
@@ -1701,7 +1758,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>86.79</v>
@@ -1715,7 +1772,7 @@
         <v>11</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>88.73</v>
@@ -1723,86 +1780,86 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>86.41</v>
+        <v>80.68</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>87.19</v>
+        <v>88.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>87.63</v>
+        <v>86.41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>86.27</v>
+        <v>87.19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>84.43</v>
+        <v>87.63</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>87.38</v>
+        <v>86.27</v>
       </c>
     </row>
     <row r="42">
@@ -1813,7 +1870,7 @@
         <v>11</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>87.6</v>
@@ -1827,7 +1884,7 @@
         <v>11</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>87.55</v>
@@ -1840,7 +1897,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -1855,10 +1912,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
@@ -1866,7 +1923,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>91.65</v>
@@ -1877,7 +1934,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>53.07</v>
@@ -1888,7 +1945,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>22.46</v>
@@ -1899,7 +1956,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>93.67</v>
@@ -1910,7 +1967,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>94.91</v>
@@ -1921,7 +1978,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>87.26</v>
@@ -1932,7 +1989,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>86.58</v>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_metropolitana.xlsx
@@ -70,7 +70,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:40</t>
+    <t xml:space="preserve">2026-09-23 16:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_metropolitana.xlsx
@@ -70,7 +70,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 16:23</t>
+    <t xml:space="preserve">2026-10-05 05:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
